--- a/2A202601654_DoThiThanhLoan_Day24.xlsx
+++ b/2A202601654_DoThiThanhLoan_Day24.xlsx
@@ -847,7 +847,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1054,6 +1054,9 @@
     </xf>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2206,10 +2209,13 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="24.75" customHeight="1">
-      <c r="B39" s="52" t="inlineStr">
-        <is>
-          <t>Tại sao bạn chọn mức ARPU và CAC như trên? Logic gì để bảo vệ những con số này trước nhà đầu tư? Viết 2-3 câu...</t>
+    <row r="39" ht="95" customHeight="1">
+      <c r="B39" s="79" t="inlineStr">
+        <is>
+          <t>AttendAI đặt ARPU 1.600.000 VNĐ/khách/tháng theo mô hình Hybrid: 590.000 phí nền tảng cộng 18.000/nhân viên. Với khách trung bình 55 lao động, mức này cao hơn ~15% so với ACheckin gói Starter (25.000 VNĐ/nhân viên/tháng) — phần chênh đổi lấy lớp AI nhận diện khuôn mặt chống chấm công hộ mà gói phổ thông không có. CAC 6.000.000 VNĐ tương đương 3,75 tháng doanh thu, đã tính đủ lương inside-sales, quảng cáo, demo và onboarding, không chỉ riêng tiền ads.
+Về AI Hidden Costs, chúng tôi dự trù 190.000 VNĐ/khách/tháng, bằng 59% chi phí API (320.000): data labeling cho ~5% lượt nhận diện bị nghi ngờ (55.000), retrain model 20%/năm phân bổ đầu khách (45.000), Human-in-the-loop QA duyệt ca bất thường ~1,2 giờ/khách/tháng (65.000), và compliance dữ liệu sinh trắc học theo Nghị định 13/2023 (25.000). Vì vậy Gross Margin chỉ 60% — đúng khoảng 40-60% của sản phẩm AI, không phải 80% kiểu SaaS truyền thống.
+Kết quả Base: LTV/CAC 5,33 và CAC Payback 6,25 tháng, vượt tiêu chuẩn VC. Tỷ số này không đến từ việc bóp CAC xuống thấp mà từ vòng đời khách 33 tháng — hệ quả của switching cost cao: đổi phần mềm chấm công đồng nghĩa di chuyển toàn bộ dữ liệu công và làm lại tích hợp bảng lương. NPV 927 triệu, IRR 43,6%, hoàn vốn dự án tháng 21.
+Rủi ro lớn nhất là tiền mặt chạm đáy 529 triệu ở tháng 9, chỉ bằng 3 tháng chi phí cố định. Trong kịch bản Pessimistic với Churn 4,5% và CAC 9 triệu (đều gấp 1,5 lần Base), Runway vẫn đạt 14 tháng nhờ ba hành động đã định lượng: dừng acquisition trả phí (81 xuống 16 khách mới/tháng), đóng băng tuyển dụng, cắt ngân sách brand.</t>
         </is>
       </c>
       <c r="C39" s="61" t="n"/>
@@ -2217,10 +2223,10 @@
       <c r="E39" s="61" t="n"/>
       <c r="F39" s="61" t="n"/>
     </row>
-    <row r="40" ht="24.75" customHeight="1">
+    <row r="40" ht="95" customHeight="1">
       <c r="B40" s="62" t="n"/>
     </row>
-    <row r="41" ht="24.75" customHeight="1">
+    <row r="41" ht="95" customHeight="1">
       <c r="B41" s="62" t="n"/>
     </row>
   </sheetData>
@@ -2697,7 +2703,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Pessimistic</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D4" s="45" t="inlineStr">

--- a/2A202601654_DoThiThanhLoan_Day24.xlsx
+++ b/2A202601654_DoThiThanhLoan_Day24.xlsx
@@ -3,12 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="24360" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="23040" windowHeight="8400" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Assumptions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Unit Economics" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. P&amp;L &amp; ROI" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Sensitivity" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -17,12 +18,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="165" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0&quot; tháng&quot;"/>
     <numFmt numFmtId="167" formatCode="0.00\x"/>
     <numFmt numFmtId="168" formatCode="0.00%;\(0.00%\);\-"/>
+    <numFmt numFmtId="169" formatCode="0.0%"/>
+    <numFmt numFmtId="170" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="41">
     <font>
@@ -594,6 +597,24 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCBD5E1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -691,24 +712,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFCBD5E1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFCBD5E1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -723,7 +726,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="6" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1">
@@ -735,34 +738,34 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="10" borderId="7" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="9" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="11" borderId="8" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="11" borderId="10" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="11" borderId="7" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="11" borderId="9" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="12" borderId="9" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="11" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="10" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="12" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="11" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="13" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="13" borderId="0" applyAlignment="1">
@@ -847,7 +850,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -879,18 +882,23 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -903,6 +911,7 @@
     <xf numFmtId="164" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -925,24 +934,28 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="12" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="12" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -958,47 +971,36 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="12" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1011,8 +1013,6 @@
     <xf numFmtId="165" fontId="12" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1055,8 +1055,35 @@
     <xf numFmtId="164" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="169" fontId="12" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="12" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1071,7 +1098,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1110,7 +1137,7 @@
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="28">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -1164,6 +1191,36 @@
         <b val="1"/>
         <color rgb="FFDC2626"/>
         <sz val="9"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFEE2E2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FF16A34A"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFDCFCE7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FFDC2626"/>
+        <sz val="11"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -1391,28 +1448,52 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDCFCE7"/>
+          <bgColor rgb="FFDCFCE7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEF3C7"/>
+          <bgColor rgb="FFFEF3C7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEE2E2"/>
+          <bgColor rgb="FFFEE2E2"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
-      <tableStyleElement type="wholeTable" dxfId="12"/>
-      <tableStyleElement type="headerRow" dxfId="11"/>
-      <tableStyleElement type="totalRow" dxfId="10"/>
-      <tableStyleElement type="firstColumn" dxfId="9"/>
-      <tableStyleElement type="lastColumn" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="wholeTable" dxfId="14"/>
+      <tableStyleElement type="headerRow" dxfId="13"/>
+      <tableStyleElement type="totalRow" dxfId="12"/>
+      <tableStyleElement type="firstColumn" dxfId="11"/>
+      <tableStyleElement type="lastColumn" dxfId="10"/>
+      <tableStyleElement type="firstRowStripe" dxfId="9"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="8"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
-      <tableStyleElement type="headerRow" dxfId="22"/>
-      <tableStyleElement type="totalRow" dxfId="21"/>
-      <tableStyleElement type="firstRowStripe" dxfId="20"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="19"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="18"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="17"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="16"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="15"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="14"/>
-      <tableStyleElement type="pageFieldValues" dxfId="13"/>
+      <tableStyleElement type="headerRow" dxfId="24"/>
+      <tableStyleElement type="totalRow" dxfId="23"/>
+      <tableStyleElement type="firstRowStripe" dxfId="22"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="21"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="20"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="19"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="18"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="17"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="16"/>
+      <tableStyleElement type="pageFieldValues" dxfId="15"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -1669,7 +1750,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:G41"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.675925925925929" defaultRowHeight="14.4"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
@@ -1686,7 +1767,7 @@
       </c>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="B3" s="45" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Luật chơi: chỉ điền vào các ô MÀU VÀNG. Các ô khác là công thức và sẽ tự tính.</t>
         </is>
@@ -1710,95 +1791,95 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="E6" s="42" t="inlineStr">
+      <c r="E6" s="35" t="inlineStr">
         <is>
           <t>Pessimistic</t>
         </is>
       </c>
-      <c r="F6" s="43" t="inlineStr">
+      <c r="F6" s="36" t="inlineStr">
         <is>
           <t>Đơn vị</t>
         </is>
       </c>
-      <c r="G6" s="17" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>Ghi chú / Note</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>ARPU — Giá bán bình quân/khách/tháng</t>
         </is>
       </c>
-      <c r="C7" s="54" t="n">
+      <c r="C7" s="55" t="n">
         <v>1900000</v>
       </c>
-      <c r="D7" s="54" t="n">
+      <c r="D7" s="55" t="n">
         <v>1600000</v>
       </c>
-      <c r="E7" s="54" t="n">
+      <c r="E7" s="55" t="n">
         <v>1300000</v>
       </c>
-      <c r="F7" s="44" t="inlineStr">
+      <c r="F7" s="38" t="inlineStr">
         <is>
           <t>VND</t>
         </is>
       </c>
-      <c r="G7" s="45" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>Pricing cao hơn → khó bán hơn nhưng margin tốt hơn</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>Adoption rate — % TAM chuyển thành khách/tháng</t>
         </is>
       </c>
-      <c r="C8" s="55" t="n">
+      <c r="C8" s="56" t="n">
         <v>0.0035</v>
       </c>
-      <c r="D8" s="55" t="n">
+      <c r="D8" s="56" t="n">
         <v>0.003</v>
       </c>
-      <c r="E8" s="56" t="n">
+      <c r="E8" s="57" t="n">
         <v>0.0008</v>
       </c>
-      <c r="F8" s="44" t="inlineStr">
+      <c r="F8" s="38" t="inlineStr">
         <is>
           <t>%/tháng</t>
         </is>
       </c>
-      <c r="G8" s="45" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>% TAM chuyển thành khách trả tiền mới mỗi tháng</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Total addressable market (số khách tiềm năng)</t>
         </is>
       </c>
-      <c r="C9" s="54" t="n">
+      <c r="C9" s="55" t="n">
         <v>35000</v>
       </c>
-      <c r="D9" s="54" t="n">
+      <c r="D9" s="55" t="n">
         <v>27000</v>
       </c>
-      <c r="E9" s="54" t="n">
+      <c r="E9" s="55" t="n">
         <v>20000</v>
       </c>
-      <c r="F9" s="44" t="inlineStr">
+      <c r="F9" s="38" t="inlineStr">
         <is>
           <t>khách</t>
         </is>
       </c>
-      <c r="G9" s="45" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>Tổng số khách hàng tiềm năng có thể tiếp cận được</t>
         </is>
@@ -1812,78 +1893,78 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>API cost / khách / tháng</t>
         </is>
       </c>
-      <c r="C12" s="54" t="n">
+      <c r="C12" s="55" t="n">
         <v>290000</v>
       </c>
-      <c r="D12" s="54" t="n">
+      <c r="D12" s="55" t="n">
         <v>320000</v>
       </c>
-      <c r="E12" s="54" t="n">
+      <c r="E12" s="55" t="n">
         <v>380000</v>
       </c>
-      <c r="F12" s="44" t="inlineStr">
+      <c r="F12" s="38" t="inlineStr">
         <is>
           <t>VND</t>
         </is>
       </c>
-      <c r="G12" s="45" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>Tiền gọi OpenAI/Anthropic/Gemini API</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>Hidden costs (labeling, retraining, QA)</t>
         </is>
       </c>
-      <c r="C13" s="54" t="n">
+      <c r="C13" s="55" t="n">
         <v>150000</v>
       </c>
-      <c r="D13" s="54" t="n">
+      <c r="D13" s="55" t="n">
         <v>190000</v>
       </c>
-      <c r="E13" s="54" t="n">
+      <c r="E13" s="55" t="n">
         <v>240000</v>
       </c>
-      <c r="F13" s="44" t="inlineStr">
+      <c r="F13" s="38" t="inlineStr">
         <is>
           <t>VND</t>
         </is>
       </c>
-      <c r="G13" s="45" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>Đừng quên! Đây là cục giết startup AI</t>
         </is>
       </c>
     </row>
     <row r="14" ht="17.55" customHeight="1">
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>Infrastructure (server/cloud) / khách</t>
         </is>
       </c>
-      <c r="C14" s="54" t="n">
+      <c r="C14" s="55" t="n">
         <v>120000</v>
       </c>
-      <c r="D14" s="54" t="n">
+      <c r="D14" s="55" t="n">
         <v>130000</v>
       </c>
-      <c r="E14" s="54" t="n">
+      <c r="E14" s="55" t="n">
         <v>150000</v>
       </c>
-      <c r="F14" s="44" t="inlineStr">
+      <c r="F14" s="38" t="inlineStr">
         <is>
           <t>VND</t>
         </is>
       </c>
-      <c r="G14" s="45" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>Phần allocate cloud cost cho mỗi khách</t>
         </is>
@@ -1895,19 +1976,19 @@
           <t>→ Tổng COGS / khách / tháng</t>
         </is>
       </c>
-      <c r="C15" s="57">
+      <c r="C15" s="58">
         <f>C12+C13+C14</f>
         <v/>
       </c>
-      <c r="D15" s="57">
+      <c r="D15" s="58">
         <f>D12+D13+D14</f>
         <v/>
       </c>
-      <c r="E15" s="57">
+      <c r="E15" s="58">
         <f>E12+E13+E14</f>
         <v/>
       </c>
-      <c r="F15" s="53" t="n"/>
+      <c r="F15" s="51" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="10" t="inlineStr">
@@ -1917,50 +1998,50 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>Monthly Churn Rate — % khách rời mỗi tháng</t>
         </is>
       </c>
-      <c r="C18" s="56" t="n">
+      <c r="C18" s="57" t="n">
         <v>0.02</v>
       </c>
-      <c r="D18" s="56" t="n">
+      <c r="D18" s="57" t="n">
         <v>0.03</v>
       </c>
-      <c r="E18" s="56" t="n">
+      <c r="E18" s="57" t="n">
         <v>0.045</v>
       </c>
-      <c r="F18" s="44" t="inlineStr">
+      <c r="F18" s="38" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G18" s="45" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>Benchmark AI product &lt; 5%/tháng</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>→ Số tháng ở lại trung bình</t>
         </is>
       </c>
-      <c r="C19" s="58">
+      <c r="C19" s="59">
         <f>IFERROR(1/C18,0)</f>
         <v/>
       </c>
-      <c r="D19" s="58">
+      <c r="D19" s="59">
         <f>IFERROR(1/D18,0)</f>
         <v/>
       </c>
-      <c r="E19" s="58">
+      <c r="E19" s="59">
         <f>IFERROR(1/E18,0)</f>
         <v/>
       </c>
-      <c r="F19" s="46" t="n"/>
+      <c r="F19" s="40" t="n"/>
     </row>
     <row r="21">
       <c r="B21" s="10" t="inlineStr">
@@ -1970,26 +2051,26 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>CAC — Tổng chi phí có 1 khách hàng mới</t>
         </is>
       </c>
-      <c r="C22" s="54" t="n">
+      <c r="C22" s="55" t="n">
         <v>5000000</v>
       </c>
-      <c r="D22" s="54" t="n">
+      <c r="D22" s="55" t="n">
         <v>6000000</v>
       </c>
-      <c r="E22" s="54" t="n">
+      <c r="E22" s="55" t="n">
         <v>9000000</v>
       </c>
-      <c r="F22" s="44" t="inlineStr">
+      <c r="F22" s="38" t="inlineStr">
         <is>
           <t>VND</t>
         </is>
       </c>
-      <c r="G22" s="45" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>Tổng tiền Marketing &amp; Sales / Số khách mới</t>
         </is>
@@ -2003,92 +2084,92 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>Salaries — Lương team (PM/Dev/Designer)</t>
         </is>
       </c>
-      <c r="C25" s="54" t="n">
+      <c r="C25" s="55" t="n">
         <v>180000000</v>
       </c>
-      <c r="D25" s="54" t="n">
+      <c r="D25" s="55" t="n">
         <v>130000000</v>
       </c>
-      <c r="E25" s="54" t="n">
+      <c r="E25" s="55" t="n">
         <v>110000000</v>
       </c>
-      <c r="F25" s="44" t="inlineStr">
+      <c r="F25" s="38" t="inlineStr">
         <is>
           <t>VND/tháng</t>
         </is>
       </c>
-      <c r="G25" s="45" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>Pessimistic = phải hire thêm nếu khó scale</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>Office, tools, admin</t>
         </is>
       </c>
-      <c r="C26" s="54" t="n">
+      <c r="C26" s="55" t="n">
         <v>30000000</v>
       </c>
-      <c r="D26" s="54" t="n">
+      <c r="D26" s="55" t="n">
         <v>25000000</v>
       </c>
-      <c r="E26" s="54" t="n">
+      <c r="E26" s="55" t="n">
         <v>20000000</v>
       </c>
-      <c r="F26" s="44" t="inlineStr">
+      <c r="F26" s="38" t="inlineStr">
         <is>
           <t>VND/tháng</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>Marketing budget hàng tháng</t>
         </is>
       </c>
-      <c r="C27" s="54" t="n">
+      <c r="C27" s="55" t="n">
         <v>30000000</v>
       </c>
-      <c r="D27" s="54" t="n">
+      <c r="D27" s="55" t="n">
         <v>15000000</v>
       </c>
-      <c r="E27" s="54" t="n">
+      <c r="E27" s="55" t="n">
         <v>3000000</v>
       </c>
-      <c r="F27" s="44" t="inlineStr">
+      <c r="F27" s="38" t="inlineStr">
         <is>
           <t>VND/tháng</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="19" t="inlineStr">
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>→ Tổng Fixed Cost / tháng</t>
         </is>
       </c>
-      <c r="C28" s="59">
+      <c r="C28" s="60">
         <f>SUM(C25:C27)</f>
         <v/>
       </c>
-      <c r="D28" s="59">
+      <c r="D28" s="60">
         <f>SUM(D25:D27)</f>
         <v/>
       </c>
-      <c r="E28" s="59">
+      <c r="E28" s="60">
         <f>SUM(E25:E27)</f>
         <v/>
       </c>
-      <c r="F28" s="46" t="n"/>
+      <c r="F28" s="40" t="n"/>
     </row>
     <row r="30">
       <c r="B30" s="10" t="inlineStr">
@@ -2098,52 +2179,52 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="13" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>Vốn đầu tư ban đầu (build MVP, setup)</t>
         </is>
       </c>
-      <c r="C31" s="54" t="n">
+      <c r="C31" s="55" t="n">
         <v>800000000</v>
       </c>
-      <c r="D31" s="54" t="n">
+      <c r="D31" s="55" t="n">
         <v>800000000</v>
       </c>
-      <c r="E31" s="54" t="n">
+      <c r="E31" s="55" t="n">
         <v>800000000</v>
       </c>
-      <c r="F31" s="44" t="inlineStr">
+      <c r="F31" s="38" t="inlineStr">
         <is>
           <t>VND</t>
         </is>
       </c>
-      <c r="G31" s="45" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>Chi phí 1 lần — lương team build MVP, infrastructure setup</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="13" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>Tiền mặt ban đầu (sau khi đã trừ vốn đầu tư)</t>
         </is>
       </c>
-      <c r="C32" s="54" t="n">
+      <c r="C32" s="55" t="n">
         <v>4000000000</v>
       </c>
-      <c r="D32" s="54" t="n">
+      <c r="D32" s="55" t="n">
         <v>4000000000</v>
       </c>
-      <c r="E32" s="54" t="n">
+      <c r="E32" s="55" t="n">
         <v>4000000000</v>
       </c>
-      <c r="F32" s="44" t="inlineStr">
+      <c r="F32" s="38" t="inlineStr">
         <is>
           <t>VND</t>
         </is>
       </c>
-      <c r="G32" s="45" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>Số tiền có sẵn để chi trả fixed cost trong giai đoạn đầu</t>
         </is>
@@ -2157,50 +2238,50 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>Annual discount rate (WACC)</t>
         </is>
       </c>
-      <c r="C35" s="56" t="n">
+      <c r="C35" s="57" t="n">
         <v>0.2</v>
       </c>
-      <c r="D35" s="56" t="n">
+      <c r="D35" s="57" t="n">
         <v>0.2</v>
       </c>
-      <c r="E35" s="56" t="n">
+      <c r="E35" s="57" t="n">
         <v>0.2</v>
       </c>
-      <c r="F35" s="44" t="inlineStr">
+      <c r="F35" s="38" t="inlineStr">
         <is>
           <t>%/năm</t>
         </is>
       </c>
-      <c r="G35" s="45" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>Mức kỳ vọng tối thiểu của nhà đầu tư cho dự án AI rủi ro</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="19" t="inlineStr">
+      <c r="B36" s="22" t="inlineStr">
         <is>
           <t>→ Monthly discount rate</t>
         </is>
       </c>
-      <c r="C36" s="60">
+      <c r="C36" s="61">
         <f>(1+C35)^(1/12)-1</f>
         <v/>
       </c>
-      <c r="D36" s="60">
+      <c r="D36" s="61">
         <f>(1+D35)^(1/12)-1</f>
         <v/>
       </c>
-      <c r="E36" s="60">
+      <c r="E36" s="61">
         <f>(1+E35)^(1/12)-1</f>
         <v/>
       </c>
-      <c r="F36" s="46" t="n"/>
+      <c r="F36" s="40" t="n"/>
     </row>
     <row r="38">
       <c r="B38" s="10" t="inlineStr">
@@ -2210,7 +2291,7 @@
       </c>
     </row>
     <row r="39" ht="95" customHeight="1">
-      <c r="B39" s="79" t="inlineStr">
+      <c r="B39" s="52" t="inlineStr">
         <is>
           <t>AttendAI đặt ARPU 1.600.000 VNĐ/khách/tháng theo mô hình Hybrid: 590.000 phí nền tảng cộng 18.000/nhân viên. Với khách trung bình 55 lao động, mức này cao hơn ~15% so với ACheckin gói Starter (25.000 VNĐ/nhân viên/tháng) — phần chênh đổi lấy lớp AI nhận diện khuôn mặt chống chấm công hộ mà gói phổ thông không có. CAC 6.000.000 VNĐ tương đương 3,75 tháng doanh thu, đã tính đủ lương inside-sales, quảng cáo, demo và onboarding, không chỉ riêng tiền ads.
 Về AI Hidden Costs, chúng tôi dự trù 190.000 VNĐ/khách/tháng, bằng 59% chi phí API (320.000): data labeling cho ~5% lượt nhận diện bị nghi ngờ (55.000), retrain model 20%/năm phân bổ đầu khách (45.000), Human-in-the-loop QA duyệt ca bất thường ~1,2 giờ/khách/tháng (65.000), và compliance dữ liệu sinh trắc học theo Nghị định 13/2023 (25.000). Vì vậy Gross Margin chỉ 60% — đúng khoảng 40-60% của sản phẩm AI, không phải 80% kiểu SaaS truyền thống.
@@ -2218,16 +2299,16 @@
 Rủi ro lớn nhất là tiền mặt chạm đáy 529 triệu ở tháng 9, chỉ bằng 3 tháng chi phí cố định. Trong kịch bản Pessimistic với Churn 4,5% và CAC 9 triệu (đều gấp 1,5 lần Base), Runway vẫn đạt 14 tháng nhờ ba hành động đã định lượng: dừng acquisition trả phí (81 xuống 16 khách mới/tháng), đóng băng tuyển dụng, cắt ngân sách brand.</t>
         </is>
       </c>
-      <c r="C39" s="61" t="n"/>
-      <c r="D39" s="61" t="n"/>
-      <c r="E39" s="61" t="n"/>
-      <c r="F39" s="61" t="n"/>
+      <c r="C39" s="53" t="n"/>
+      <c r="D39" s="53" t="n"/>
+      <c r="E39" s="53" t="n"/>
+      <c r="F39" s="53" t="n"/>
     </row>
     <row r="40" ht="95" customHeight="1">
-      <c r="B40" s="62" t="n"/>
+      <c r="B40" s="54" t="n"/>
     </row>
     <row r="41" ht="95" customHeight="1">
-      <c r="B41" s="62" t="n"/>
+      <c r="B41" s="54" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -2255,7 +2336,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:G25"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.675925925925929" defaultRowHeight="14.4"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
@@ -2272,14 +2353,14 @@
       </c>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="B3" s="45" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Tự động tính từ Tab 1. Kiểm tra: LTV/CAC &gt; 3 (Base) và CAC Payback &lt; 12 tháng.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>Chỉ số</t>
         </is>
@@ -2294,17 +2375,17 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="E5" s="42" t="inlineStr">
+      <c r="E5" s="35" t="inlineStr">
         <is>
           <t>Pessimistic</t>
         </is>
       </c>
-      <c r="F5" s="43" t="inlineStr">
+      <c r="F5" s="36" t="inlineStr">
         <is>
           <t>Đơn vị</t>
         </is>
       </c>
-      <c r="G5" s="17" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>Benchmark / Note</t>
         </is>
@@ -2318,98 +2399,98 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>ARPU / tháng</t>
         </is>
       </c>
-      <c r="C8" s="63">
+      <c r="C8" s="62">
         <f>'1. Assumptions'!C7</f>
         <v/>
       </c>
-      <c r="D8" s="63">
+      <c r="D8" s="62">
         <f>'1. Assumptions'!D7</f>
         <v/>
       </c>
-      <c r="E8" s="63">
+      <c r="E8" s="62">
         <f>'1. Assumptions'!E7</f>
         <v/>
       </c>
-      <c r="F8" s="44" t="inlineStr">
+      <c r="F8" s="38" t="inlineStr">
         <is>
           <t>VND</t>
         </is>
       </c>
-      <c r="G8" s="45" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Liên kết từ Tab Assumptions</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>COGS / tháng</t>
         </is>
       </c>
-      <c r="C9" s="63">
+      <c r="C9" s="62">
         <f>'1. Assumptions'!C15</f>
         <v/>
       </c>
-      <c r="D9" s="63">
+      <c r="D9" s="62">
         <f>'1. Assumptions'!D15</f>
         <v/>
       </c>
-      <c r="E9" s="63">
+      <c r="E9" s="62">
         <f>'1. Assumptions'!E15</f>
         <v/>
       </c>
-      <c r="F9" s="44" t="inlineStr">
+      <c r="F9" s="38" t="inlineStr">
         <is>
           <t>VND</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>→ Gross Profit / tháng</t>
         </is>
       </c>
-      <c r="C10" s="59">
+      <c r="C10" s="60">
         <f>C8-C9</f>
         <v/>
       </c>
-      <c r="D10" s="59">
+      <c r="D10" s="60">
         <f>D8-D9</f>
         <v/>
       </c>
-      <c r="E10" s="59">
+      <c r="E10" s="60">
         <f>E8-E9</f>
         <v/>
       </c>
-      <c r="F10" s="46" t="n"/>
+      <c r="F10" s="40" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>→ Gross Margin %</t>
         </is>
       </c>
-      <c r="C11" s="60">
+      <c r="C11" s="61">
         <f>IFERROR(C10/C8,0)</f>
         <v/>
       </c>
-      <c r="D11" s="60">
+      <c r="D11" s="61">
         <f>IFERROR(D10/D8,0)</f>
         <v/>
       </c>
-      <c r="E11" s="60">
+      <c r="E11" s="61">
         <f>IFERROR(E10/E8,0)</f>
         <v/>
       </c>
-      <c r="F11" s="46" t="n"/>
-      <c r="G11" s="45" t="inlineStr">
+      <c r="F11" s="40" t="n"/>
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>AI product target: 40-60%. SaaS truyền thống: 80%+</t>
         </is>
@@ -2423,49 +2504,49 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>Số tháng ở lại trung bình</t>
         </is>
       </c>
-      <c r="C14" s="64">
+      <c r="C14" s="63">
         <f>'1. Assumptions'!C19</f>
         <v/>
       </c>
-      <c r="D14" s="64">
+      <c r="D14" s="63">
         <f>'1. Assumptions'!D19</f>
         <v/>
       </c>
-      <c r="E14" s="64">
+      <c r="E14" s="63">
         <f>'1. Assumptions'!E19</f>
         <v/>
       </c>
-      <c r="F14" s="44" t="inlineStr">
+      <c r="F14" s="38" t="inlineStr">
         <is>
           <t>tháng</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="19" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>→ LTV = Gross Profit × Số tháng ở lại</t>
         </is>
       </c>
-      <c r="C15" s="59">
+      <c r="C15" s="60">
         <f>C10*C14</f>
         <v/>
       </c>
-      <c r="D15" s="59">
+      <c r="D15" s="60">
         <f>D10*D14</f>
         <v/>
       </c>
-      <c r="E15" s="59">
+      <c r="E15" s="60">
         <f>E10*E14</f>
         <v/>
       </c>
-      <c r="F15" s="46" t="n"/>
-      <c r="G15" s="45" t="inlineStr">
+      <c r="F15" s="40" t="n"/>
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>Tổng lợi nhuận gộp một khách mang lại trong vòng đời</t>
         </is>
@@ -2479,24 +2560,24 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>CAC — Chi phí thu hút 1 khách</t>
         </is>
       </c>
-      <c r="C18" s="63">
+      <c r="C18" s="62">
         <f>'1. Assumptions'!C22</f>
         <v/>
       </c>
-      <c r="D18" s="63">
+      <c r="D18" s="62">
         <f>'1. Assumptions'!D22</f>
         <v/>
       </c>
-      <c r="E18" s="63">
+      <c r="E18" s="62">
         <f>'1. Assumptions'!E22</f>
         <v/>
       </c>
-      <c r="F18" s="44" t="inlineStr">
+      <c r="F18" s="38" t="inlineStr">
         <is>
           <t>VND</t>
         </is>
@@ -2510,50 +2591,50 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>→ LTV / CAC Ratio</t>
         </is>
       </c>
-      <c r="C21" s="65">
+      <c r="C21" s="64">
         <f>IFERROR(C15/C18,0)</f>
         <v/>
       </c>
-      <c r="D21" s="65">
+      <c r="D21" s="64">
         <f>IFERROR(D15/D18,0)</f>
         <v/>
       </c>
-      <c r="E21" s="65">
+      <c r="E21" s="64">
         <f>IFERROR(E15/E18,0)</f>
         <v/>
       </c>
-      <c r="F21" s="46" t="n"/>
-      <c r="G21" s="45" t="inlineStr">
+      <c r="F21" s="40" t="n"/>
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>🎯 Target &gt; 3.0x (tiêu chuẩn vàng VC)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>→ CAC Payback Period</t>
         </is>
       </c>
-      <c r="C22" s="58">
+      <c r="C22" s="59">
         <f>IFERROR(C18/C10,0)</f>
         <v/>
       </c>
-      <c r="D22" s="58">
+      <c r="D22" s="59">
         <f>IFERROR(D18/D10,0)</f>
         <v/>
       </c>
-      <c r="E22" s="58">
+      <c r="E22" s="59">
         <f>IFERROR(E18/E10,0)</f>
         <v/>
       </c>
-      <c r="F22" s="46" t="n"/>
-      <c r="G22" s="45" t="inlineStr">
+      <c r="F22" s="40" t="n"/>
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>🎯 Target &lt; 12 tháng (early-stage)</t>
         </is>
@@ -2567,20 +2648,20 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="17" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>Unit Economics Status</t>
         </is>
       </c>
-      <c r="C25" s="41">
+      <c r="C25" s="45">
         <f>IF(AND(C21&gt;=3,C22&lt;=12),"✓ HEALTHY",IF(OR(C21&lt;1,C22&gt;18),"✗ UNHEALTHY","⚠ WATCH"))</f>
         <v/>
       </c>
-      <c r="D25" s="41">
+      <c r="D25" s="45">
         <f>IF(AND(D21&gt;=3,D22&lt;=12),"✓ HEALTHY",IF(OR(D21&lt;1,D22&gt;18),"✗ UNHEALTHY","⚠ WATCH"))</f>
         <v/>
       </c>
-      <c r="E25" s="41">
+      <c r="E25" s="45">
         <f>IF(AND(E21&gt;=3,E22&lt;=12),"✓ HEALTHY",IF(OR(E21&lt;1,E22&gt;18),"✗ UNHEALTHY","⚠ WATCH"))</f>
         <v/>
       </c>
@@ -2679,7 +2760,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:AA44"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.675925925925929" defaultRowHeight="14.4"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
@@ -2706,7 +2787,7 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Đổi scenario tại đây để toàn bộ P&amp;L tự cập nhật</t>
         </is>
@@ -2737,7 +2818,7 @@
           <t>ARPU / khách / tháng</t>
         </is>
       </c>
-      <c r="C8" s="66">
+      <c r="C8" s="65">
         <f>CHOOSE($C$6,'1. Assumptions'!C7,'1. Assumptions'!D7,'1. Assumptions'!E7)</f>
         <v/>
       </c>
@@ -2748,7 +2829,7 @@
           <t>Adoption rate</t>
         </is>
       </c>
-      <c r="C9" s="67">
+      <c r="C9" s="66">
         <f>CHOOSE($C$6,'1. Assumptions'!C8,'1. Assumptions'!D8,'1. Assumptions'!E8)</f>
         <v/>
       </c>
@@ -2759,7 +2840,7 @@
           <t>TAM (số khách tiềm năng)</t>
         </is>
       </c>
-      <c r="C10" s="66">
+      <c r="C10" s="65">
         <f>CHOOSE($C$6,'1. Assumptions'!C9,'1. Assumptions'!D9,'1. Assumptions'!E9)</f>
         <v/>
       </c>
@@ -2770,7 +2851,7 @@
           <t>Total COGS / khách</t>
         </is>
       </c>
-      <c r="C11" s="66">
+      <c r="C11" s="65">
         <f>CHOOSE($C$6,'1. Assumptions'!C15,'1. Assumptions'!D15,'1. Assumptions'!E15)</f>
         <v/>
       </c>
@@ -2781,7 +2862,7 @@
           <t>Monthly Churn Rate</t>
         </is>
       </c>
-      <c r="C12" s="67">
+      <c r="C12" s="66">
         <f>CHOOSE($C$6,'1. Assumptions'!C18,'1. Assumptions'!D18,'1. Assumptions'!E18)</f>
         <v/>
       </c>
@@ -2792,7 +2873,7 @@
           <t>CAC / khách mới</t>
         </is>
       </c>
-      <c r="C13" s="66">
+      <c r="C13" s="65">
         <f>CHOOSE($C$6,'1. Assumptions'!C22,'1. Assumptions'!D22,'1. Assumptions'!E22)</f>
         <v/>
       </c>
@@ -2803,7 +2884,7 @@
           <t>Fixed Cost / tháng</t>
         </is>
       </c>
-      <c r="C14" s="66">
+      <c r="C14" s="65">
         <f>CHOOSE($C$6,'1. Assumptions'!C28,'1. Assumptions'!D28,'1. Assumptions'!E28)</f>
         <v/>
       </c>
@@ -2814,7 +2895,7 @@
           <t>Initial Investment</t>
         </is>
       </c>
-      <c r="C15" s="66">
+      <c r="C15" s="65">
         <f>CHOOSE($C$6,'1. Assumptions'!C31,'1. Assumptions'!D31,'1. Assumptions'!E31)</f>
         <v/>
       </c>
@@ -2825,7 +2906,7 @@
           <t>Initial Cash</t>
         </is>
       </c>
-      <c r="C16" s="66">
+      <c r="C16" s="65">
         <f>CHOOSE($C$6,'1. Assumptions'!C32,'1. Assumptions'!D32,'1. Assumptions'!E32)</f>
         <v/>
       </c>
@@ -2836,7 +2917,7 @@
           <t>Monthly Discount Rate</t>
         </is>
       </c>
-      <c r="C17" s="67">
+      <c r="C17" s="66">
         <f>CHOOSE($C$6,'1. Assumptions'!C36,'1. Assumptions'!D36,'1. Assumptions'!E36)</f>
         <v/>
       </c>
@@ -2974,1070 +3055,1070 @@
           <t>M24</t>
         </is>
       </c>
-      <c r="AA21" s="29" t="inlineStr">
+      <c r="AA21" s="13" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>New customers acquired</t>
         </is>
       </c>
-      <c r="C22" s="68">
+      <c r="C22" s="67">
         <f>ROUND($C$10*$C$9,0)</f>
         <v/>
       </c>
-      <c r="D22" s="68">
+      <c r="D22" s="67">
         <f>ROUND($C$10*$C$9,0)</f>
         <v/>
       </c>
-      <c r="E22" s="68">
+      <c r="E22" s="67">
         <f>ROUND($C$10*$C$9,0)</f>
         <v/>
       </c>
-      <c r="F22" s="68">
+      <c r="F22" s="67">
         <f>ROUND($C$10*$C$9,0)</f>
         <v/>
       </c>
-      <c r="G22" s="68">
+      <c r="G22" s="67">
         <f>ROUND($C$10*$C$9,0)</f>
         <v/>
       </c>
-      <c r="H22" s="68">
+      <c r="H22" s="67">
         <f>ROUND($C$10*$C$9,0)</f>
         <v/>
       </c>
-      <c r="I22" s="68">
+      <c r="I22" s="67">
         <f>ROUND($C$10*$C$9,0)</f>
         <v/>
       </c>
-      <c r="J22" s="68">
+      <c r="J22" s="67">
         <f>ROUND($C$10*$C$9,0)</f>
         <v/>
       </c>
-      <c r="K22" s="68">
+      <c r="K22" s="67">
         <f>ROUND($C$10*$C$9,0)</f>
         <v/>
       </c>
-      <c r="L22" s="68">
+      <c r="L22" s="67">
         <f>ROUND($C$10*$C$9,0)</f>
         <v/>
       </c>
-      <c r="M22" s="68">
+      <c r="M22" s="67">
         <f>ROUND($C$10*$C$9,0)</f>
         <v/>
       </c>
-      <c r="N22" s="68">
+      <c r="N22" s="67">
         <f>ROUND($C$10*$C$9,0)</f>
         <v/>
       </c>
-      <c r="O22" s="68">
+      <c r="O22" s="67">
         <f>ROUND($C$10*$C$9,0)</f>
         <v/>
       </c>
-      <c r="P22" s="68">
+      <c r="P22" s="67">
         <f>ROUND($C$10*$C$9,0)</f>
         <v/>
       </c>
-      <c r="Q22" s="68">
+      <c r="Q22" s="67">
         <f>ROUND($C$10*$C$9,0)</f>
         <v/>
       </c>
-      <c r="R22" s="68">
+      <c r="R22" s="67">
         <f>ROUND($C$10*$C$9,0)</f>
         <v/>
       </c>
-      <c r="S22" s="68">
+      <c r="S22" s="67">
         <f>ROUND($C$10*$C$9,0)</f>
         <v/>
       </c>
-      <c r="T22" s="68">
+      <c r="T22" s="67">
         <f>ROUND($C$10*$C$9,0)</f>
         <v/>
       </c>
-      <c r="U22" s="68">
+      <c r="U22" s="67">
         <f>ROUND($C$10*$C$9,0)</f>
         <v/>
       </c>
-      <c r="V22" s="68">
+      <c r="V22" s="67">
         <f>ROUND($C$10*$C$9,0)</f>
         <v/>
       </c>
-      <c r="W22" s="68">
+      <c r="W22" s="67">
         <f>ROUND($C$10*$C$9,0)</f>
         <v/>
       </c>
-      <c r="X22" s="68">
+      <c r="X22" s="67">
         <f>ROUND($C$10*$C$9,0)</f>
         <v/>
       </c>
-      <c r="Y22" s="68">
+      <c r="Y22" s="67">
         <f>ROUND($C$10*$C$9,0)</f>
         <v/>
       </c>
-      <c r="Z22" s="68">
+      <c r="Z22" s="67">
         <f>ROUND($C$10*$C$9,0)</f>
         <v/>
       </c>
-      <c r="AA22" s="69">
+      <c r="AA22" s="68">
         <f>SUM(C22:Z22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>Active customers (end of month)</t>
         </is>
       </c>
-      <c r="C23" s="68">
+      <c r="C23" s="67">
         <f>C22</f>
         <v/>
       </c>
-      <c r="D23" s="68">
+      <c r="D23" s="67">
         <f>C23*(1-$C$12)+D22</f>
         <v/>
       </c>
-      <c r="E23" s="68">
+      <c r="E23" s="67">
         <f>D23*(1-$C$12)+E22</f>
         <v/>
       </c>
-      <c r="F23" s="68">
+      <c r="F23" s="67">
         <f>E23*(1-$C$12)+F22</f>
         <v/>
       </c>
-      <c r="G23" s="68">
+      <c r="G23" s="67">
         <f>F23*(1-$C$12)+G22</f>
         <v/>
       </c>
-      <c r="H23" s="68">
+      <c r="H23" s="67">
         <f>G23*(1-$C$12)+H22</f>
         <v/>
       </c>
-      <c r="I23" s="68">
+      <c r="I23" s="67">
         <f>H23*(1-$C$12)+I22</f>
         <v/>
       </c>
-      <c r="J23" s="68">
+      <c r="J23" s="67">
         <f>I23*(1-$C$12)+J22</f>
         <v/>
       </c>
-      <c r="K23" s="68">
+      <c r="K23" s="67">
         <f>J23*(1-$C$12)+K22</f>
         <v/>
       </c>
-      <c r="L23" s="68">
+      <c r="L23" s="67">
         <f>K23*(1-$C$12)+L22</f>
         <v/>
       </c>
-      <c r="M23" s="68">
+      <c r="M23" s="67">
         <f>L23*(1-$C$12)+M22</f>
         <v/>
       </c>
-      <c r="N23" s="68">
+      <c r="N23" s="67">
         <f>M23*(1-$C$12)+N22</f>
         <v/>
       </c>
-      <c r="O23" s="68">
+      <c r="O23" s="67">
         <f>N23*(1-$C$12)+O22</f>
         <v/>
       </c>
-      <c r="P23" s="68">
+      <c r="P23" s="67">
         <f>O23*(1-$C$12)+P22</f>
         <v/>
       </c>
-      <c r="Q23" s="68">
+      <c r="Q23" s="67">
         <f>P23*(1-$C$12)+Q22</f>
         <v/>
       </c>
-      <c r="R23" s="68">
+      <c r="R23" s="67">
         <f>Q23*(1-$C$12)+R22</f>
         <v/>
       </c>
-      <c r="S23" s="68">
+      <c r="S23" s="67">
         <f>R23*(1-$C$12)+S22</f>
         <v/>
       </c>
-      <c r="T23" s="68">
+      <c r="T23" s="67">
         <f>S23*(1-$C$12)+T22</f>
         <v/>
       </c>
-      <c r="U23" s="68">
+      <c r="U23" s="67">
         <f>T23*(1-$C$12)+U22</f>
         <v/>
       </c>
-      <c r="V23" s="68">
+      <c r="V23" s="67">
         <f>U23*(1-$C$12)+V22</f>
         <v/>
       </c>
-      <c r="W23" s="68">
+      <c r="W23" s="67">
         <f>V23*(1-$C$12)+W22</f>
         <v/>
       </c>
-      <c r="X23" s="68">
+      <c r="X23" s="67">
         <f>W23*(1-$C$12)+X22</f>
         <v/>
       </c>
-      <c r="Y23" s="68">
+      <c r="Y23" s="67">
         <f>X23*(1-$C$12)+Y22</f>
         <v/>
       </c>
-      <c r="Z23" s="68">
+      <c r="Z23" s="67">
         <f>Y23*(1-$C$12)+Z22</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="C25" s="70">
+      <c r="C25" s="69">
         <f>C23*$C$8</f>
         <v/>
       </c>
-      <c r="D25" s="70">
+      <c r="D25" s="69">
         <f>D23*$C$8</f>
         <v/>
       </c>
-      <c r="E25" s="70">
+      <c r="E25" s="69">
         <f>E23*$C$8</f>
         <v/>
       </c>
-      <c r="F25" s="70">
+      <c r="F25" s="69">
         <f>F23*$C$8</f>
         <v/>
       </c>
-      <c r="G25" s="70">
+      <c r="G25" s="69">
         <f>G23*$C$8</f>
         <v/>
       </c>
-      <c r="H25" s="70">
+      <c r="H25" s="69">
         <f>H23*$C$8</f>
         <v/>
       </c>
-      <c r="I25" s="70">
+      <c r="I25" s="69">
         <f>I23*$C$8</f>
         <v/>
       </c>
-      <c r="J25" s="70">
+      <c r="J25" s="69">
         <f>J23*$C$8</f>
         <v/>
       </c>
-      <c r="K25" s="70">
+      <c r="K25" s="69">
         <f>K23*$C$8</f>
         <v/>
       </c>
-      <c r="L25" s="70">
+      <c r="L25" s="69">
         <f>L23*$C$8</f>
         <v/>
       </c>
-      <c r="M25" s="70">
+      <c r="M25" s="69">
         <f>M23*$C$8</f>
         <v/>
       </c>
-      <c r="N25" s="70">
+      <c r="N25" s="69">
         <f>N23*$C$8</f>
         <v/>
       </c>
-      <c r="O25" s="70">
+      <c r="O25" s="69">
         <f>O23*$C$8</f>
         <v/>
       </c>
-      <c r="P25" s="70">
+      <c r="P25" s="69">
         <f>P23*$C$8</f>
         <v/>
       </c>
-      <c r="Q25" s="70">
+      <c r="Q25" s="69">
         <f>Q23*$C$8</f>
         <v/>
       </c>
-      <c r="R25" s="70">
+      <c r="R25" s="69">
         <f>R23*$C$8</f>
         <v/>
       </c>
-      <c r="S25" s="70">
+      <c r="S25" s="69">
         <f>S23*$C$8</f>
         <v/>
       </c>
-      <c r="T25" s="70">
+      <c r="T25" s="69">
         <f>T23*$C$8</f>
         <v/>
       </c>
-      <c r="U25" s="70">
+      <c r="U25" s="69">
         <f>U23*$C$8</f>
         <v/>
       </c>
-      <c r="V25" s="70">
+      <c r="V25" s="69">
         <f>V23*$C$8</f>
         <v/>
       </c>
-      <c r="W25" s="70">
+      <c r="W25" s="69">
         <f>W23*$C$8</f>
         <v/>
       </c>
-      <c r="X25" s="70">
+      <c r="X25" s="69">
         <f>X23*$C$8</f>
         <v/>
       </c>
-      <c r="Y25" s="70">
+      <c r="Y25" s="69">
         <f>Y23*$C$8</f>
         <v/>
       </c>
-      <c r="Z25" s="70">
+      <c r="Z25" s="69">
         <f>Z23*$C$8</f>
         <v/>
       </c>
-      <c r="AA25" s="71">
+      <c r="AA25" s="70">
         <f>SUM(C25:Z25)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>COGS (variable cost)</t>
         </is>
       </c>
-      <c r="C26" s="68">
+      <c r="C26" s="67">
         <f>C23*$C$11</f>
         <v/>
       </c>
-      <c r="D26" s="68">
+      <c r="D26" s="67">
         <f>D23*$C$11</f>
         <v/>
       </c>
-      <c r="E26" s="68">
+      <c r="E26" s="67">
         <f>E23*$C$11</f>
         <v/>
       </c>
-      <c r="F26" s="68">
+      <c r="F26" s="67">
         <f>F23*$C$11</f>
         <v/>
       </c>
-      <c r="G26" s="68">
+      <c r="G26" s="67">
         <f>G23*$C$11</f>
         <v/>
       </c>
-      <c r="H26" s="68">
+      <c r="H26" s="67">
         <f>H23*$C$11</f>
         <v/>
       </c>
-      <c r="I26" s="68">
+      <c r="I26" s="67">
         <f>I23*$C$11</f>
         <v/>
       </c>
-      <c r="J26" s="68">
+      <c r="J26" s="67">
         <f>J23*$C$11</f>
         <v/>
       </c>
-      <c r="K26" s="68">
+      <c r="K26" s="67">
         <f>K23*$C$11</f>
         <v/>
       </c>
-      <c r="L26" s="68">
+      <c r="L26" s="67">
         <f>L23*$C$11</f>
         <v/>
       </c>
-      <c r="M26" s="68">
+      <c r="M26" s="67">
         <f>M23*$C$11</f>
         <v/>
       </c>
-      <c r="N26" s="68">
+      <c r="N26" s="67">
         <f>N23*$C$11</f>
         <v/>
       </c>
-      <c r="O26" s="68">
+      <c r="O26" s="67">
         <f>O23*$C$11</f>
         <v/>
       </c>
-      <c r="P26" s="68">
+      <c r="P26" s="67">
         <f>P23*$C$11</f>
         <v/>
       </c>
-      <c r="Q26" s="68">
+      <c r="Q26" s="67">
         <f>Q23*$C$11</f>
         <v/>
       </c>
-      <c r="R26" s="68">
+      <c r="R26" s="67">
         <f>R23*$C$11</f>
         <v/>
       </c>
-      <c r="S26" s="68">
+      <c r="S26" s="67">
         <f>S23*$C$11</f>
         <v/>
       </c>
-      <c r="T26" s="68">
+      <c r="T26" s="67">
         <f>T23*$C$11</f>
         <v/>
       </c>
-      <c r="U26" s="68">
+      <c r="U26" s="67">
         <f>U23*$C$11</f>
         <v/>
       </c>
-      <c r="V26" s="68">
+      <c r="V26" s="67">
         <f>V23*$C$11</f>
         <v/>
       </c>
-      <c r="W26" s="68">
+      <c r="W26" s="67">
         <f>W23*$C$11</f>
         <v/>
       </c>
-      <c r="X26" s="68">
+      <c r="X26" s="67">
         <f>X23*$C$11</f>
         <v/>
       </c>
-      <c r="Y26" s="68">
+      <c r="Y26" s="67">
         <f>Y23*$C$11</f>
         <v/>
       </c>
-      <c r="Z26" s="68">
+      <c r="Z26" s="67">
         <f>Z23*$C$11</f>
         <v/>
       </c>
-      <c r="AA26" s="69">
+      <c r="AA26" s="68">
         <f>SUM(C26:Z26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="C27" s="72">
+      <c r="C27" s="71">
         <f>C25-C26</f>
         <v/>
       </c>
-      <c r="D27" s="72">
+      <c r="D27" s="71">
         <f>D25-D26</f>
         <v/>
       </c>
-      <c r="E27" s="72">
+      <c r="E27" s="71">
         <f>E25-E26</f>
         <v/>
       </c>
-      <c r="F27" s="72">
+      <c r="F27" s="71">
         <f>F25-F26</f>
         <v/>
       </c>
-      <c r="G27" s="72">
+      <c r="G27" s="71">
         <f>G25-G26</f>
         <v/>
       </c>
-      <c r="H27" s="72">
+      <c r="H27" s="71">
         <f>H25-H26</f>
         <v/>
       </c>
-      <c r="I27" s="72">
+      <c r="I27" s="71">
         <f>I25-I26</f>
         <v/>
       </c>
-      <c r="J27" s="72">
+      <c r="J27" s="71">
         <f>J25-J26</f>
         <v/>
       </c>
-      <c r="K27" s="72">
+      <c r="K27" s="71">
         <f>K25-K26</f>
         <v/>
       </c>
-      <c r="L27" s="72">
+      <c r="L27" s="71">
         <f>L25-L26</f>
         <v/>
       </c>
-      <c r="M27" s="72">
+      <c r="M27" s="71">
         <f>M25-M26</f>
         <v/>
       </c>
-      <c r="N27" s="72">
+      <c r="N27" s="71">
         <f>N25-N26</f>
         <v/>
       </c>
-      <c r="O27" s="72">
+      <c r="O27" s="71">
         <f>O25-O26</f>
         <v/>
       </c>
-      <c r="P27" s="72">
+      <c r="P27" s="71">
         <f>P25-P26</f>
         <v/>
       </c>
-      <c r="Q27" s="72">
+      <c r="Q27" s="71">
         <f>Q25-Q26</f>
         <v/>
       </c>
-      <c r="R27" s="72">
+      <c r="R27" s="71">
         <f>R25-R26</f>
         <v/>
       </c>
-      <c r="S27" s="72">
+      <c r="S27" s="71">
         <f>S25-S26</f>
         <v/>
       </c>
-      <c r="T27" s="72">
+      <c r="T27" s="71">
         <f>T25-T26</f>
         <v/>
       </c>
-      <c r="U27" s="72">
+      <c r="U27" s="71">
         <f>U25-U26</f>
         <v/>
       </c>
-      <c r="V27" s="72">
+      <c r="V27" s="71">
         <f>V25-V26</f>
         <v/>
       </c>
-      <c r="W27" s="72">
+      <c r="W27" s="71">
         <f>W25-W26</f>
         <v/>
       </c>
-      <c r="X27" s="72">
+      <c r="X27" s="71">
         <f>X25-X26</f>
         <v/>
       </c>
-      <c r="Y27" s="72">
+      <c r="Y27" s="71">
         <f>Y25-Y26</f>
         <v/>
       </c>
-      <c r="Z27" s="72">
+      <c r="Z27" s="71">
         <f>Z25-Z26</f>
         <v/>
       </c>
-      <c r="AA27" s="69">
+      <c r="AA27" s="68">
         <f>SUM(C27:Z27)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>Marketing/Acquisition cost</t>
         </is>
       </c>
-      <c r="C28" s="68">
+      <c r="C28" s="67">
         <f>C22*$C$13</f>
         <v/>
       </c>
-      <c r="D28" s="68">
+      <c r="D28" s="67">
         <f>D22*$C$13</f>
         <v/>
       </c>
-      <c r="E28" s="68">
+      <c r="E28" s="67">
         <f>E22*$C$13</f>
         <v/>
       </c>
-      <c r="F28" s="68">
+      <c r="F28" s="67">
         <f>F22*$C$13</f>
         <v/>
       </c>
-      <c r="G28" s="68">
+      <c r="G28" s="67">
         <f>G22*$C$13</f>
         <v/>
       </c>
-      <c r="H28" s="68">
+      <c r="H28" s="67">
         <f>H22*$C$13</f>
         <v/>
       </c>
-      <c r="I28" s="68">
+      <c r="I28" s="67">
         <f>I22*$C$13</f>
         <v/>
       </c>
-      <c r="J28" s="68">
+      <c r="J28" s="67">
         <f>J22*$C$13</f>
         <v/>
       </c>
-      <c r="K28" s="68">
+      <c r="K28" s="67">
         <f>K22*$C$13</f>
         <v/>
       </c>
-      <c r="L28" s="68">
+      <c r="L28" s="67">
         <f>L22*$C$13</f>
         <v/>
       </c>
-      <c r="M28" s="68">
+      <c r="M28" s="67">
         <f>M22*$C$13</f>
         <v/>
       </c>
-      <c r="N28" s="68">
+      <c r="N28" s="67">
         <f>N22*$C$13</f>
         <v/>
       </c>
-      <c r="O28" s="68">
+      <c r="O28" s="67">
         <f>O22*$C$13</f>
         <v/>
       </c>
-      <c r="P28" s="68">
+      <c r="P28" s="67">
         <f>P22*$C$13</f>
         <v/>
       </c>
-      <c r="Q28" s="68">
+      <c r="Q28" s="67">
         <f>Q22*$C$13</f>
         <v/>
       </c>
-      <c r="R28" s="68">
+      <c r="R28" s="67">
         <f>R22*$C$13</f>
         <v/>
       </c>
-      <c r="S28" s="68">
+      <c r="S28" s="67">
         <f>S22*$C$13</f>
         <v/>
       </c>
-      <c r="T28" s="68">
+      <c r="T28" s="67">
         <f>T22*$C$13</f>
         <v/>
       </c>
-      <c r="U28" s="68">
+      <c r="U28" s="67">
         <f>U22*$C$13</f>
         <v/>
       </c>
-      <c r="V28" s="68">
+      <c r="V28" s="67">
         <f>V22*$C$13</f>
         <v/>
       </c>
-      <c r="W28" s="68">
+      <c r="W28" s="67">
         <f>W22*$C$13</f>
         <v/>
       </c>
-      <c r="X28" s="68">
+      <c r="X28" s="67">
         <f>X22*$C$13</f>
         <v/>
       </c>
-      <c r="Y28" s="68">
+      <c r="Y28" s="67">
         <f>Y22*$C$13</f>
         <v/>
       </c>
-      <c r="Z28" s="68">
+      <c r="Z28" s="67">
         <f>Z22*$C$13</f>
         <v/>
       </c>
-      <c r="AA28" s="69">
+      <c r="AA28" s="68">
         <f>SUM(C28:Z28)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>Fixed cost (salaries + ops)</t>
         </is>
       </c>
-      <c r="C29" s="68">
+      <c r="C29" s="67">
         <f>$C$14</f>
         <v/>
       </c>
-      <c r="D29" s="68">
+      <c r="D29" s="67">
         <f>$C$14</f>
         <v/>
       </c>
-      <c r="E29" s="68">
+      <c r="E29" s="67">
         <f>$C$14</f>
         <v/>
       </c>
-      <c r="F29" s="68">
+      <c r="F29" s="67">
         <f>$C$14</f>
         <v/>
       </c>
-      <c r="G29" s="68">
+      <c r="G29" s="67">
         <f>$C$14</f>
         <v/>
       </c>
-      <c r="H29" s="68">
+      <c r="H29" s="67">
         <f>$C$14</f>
         <v/>
       </c>
-      <c r="I29" s="68">
+      <c r="I29" s="67">
         <f>$C$14</f>
         <v/>
       </c>
-      <c r="J29" s="68">
+      <c r="J29" s="67">
         <f>$C$14</f>
         <v/>
       </c>
-      <c r="K29" s="68">
+      <c r="K29" s="67">
         <f>$C$14</f>
         <v/>
       </c>
-      <c r="L29" s="68">
+      <c r="L29" s="67">
         <f>$C$14</f>
         <v/>
       </c>
-      <c r="M29" s="68">
+      <c r="M29" s="67">
         <f>$C$14</f>
         <v/>
       </c>
-      <c r="N29" s="68">
+      <c r="N29" s="67">
         <f>$C$14</f>
         <v/>
       </c>
-      <c r="O29" s="68">
+      <c r="O29" s="67">
         <f>$C$14</f>
         <v/>
       </c>
-      <c r="P29" s="68">
+      <c r="P29" s="67">
         <f>$C$14</f>
         <v/>
       </c>
-      <c r="Q29" s="68">
+      <c r="Q29" s="67">
         <f>$C$14</f>
         <v/>
       </c>
-      <c r="R29" s="68">
+      <c r="R29" s="67">
         <f>$C$14</f>
         <v/>
       </c>
-      <c r="S29" s="68">
+      <c r="S29" s="67">
         <f>$C$14</f>
         <v/>
       </c>
-      <c r="T29" s="68">
+      <c r="T29" s="67">
         <f>$C$14</f>
         <v/>
       </c>
-      <c r="U29" s="68">
+      <c r="U29" s="67">
         <f>$C$14</f>
         <v/>
       </c>
-      <c r="V29" s="68">
+      <c r="V29" s="67">
         <f>$C$14</f>
         <v/>
       </c>
-      <c r="W29" s="68">
+      <c r="W29" s="67">
         <f>$C$14</f>
         <v/>
       </c>
-      <c r="X29" s="68">
+      <c r="X29" s="67">
         <f>$C$14</f>
         <v/>
       </c>
-      <c r="Y29" s="68">
+      <c r="Y29" s="67">
         <f>$C$14</f>
         <v/>
       </c>
-      <c r="Z29" s="68">
+      <c r="Z29" s="67">
         <f>$C$14</f>
         <v/>
       </c>
-      <c r="AA29" s="69">
+      <c r="AA29" s="68">
         <f>SUM(C29:Z29)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="19" t="inlineStr">
+      <c r="B30" s="22" t="inlineStr">
         <is>
           <t>Operating Profit (EBITDA)</t>
         </is>
       </c>
-      <c r="C30" s="73">
+      <c r="C30" s="72">
         <f>C27-C28-C29</f>
         <v/>
       </c>
-      <c r="D30" s="73">
+      <c r="D30" s="72">
         <f>D27-D28-D29</f>
         <v/>
       </c>
-      <c r="E30" s="73">
+      <c r="E30" s="72">
         <f>E27-E28-E29</f>
         <v/>
       </c>
-      <c r="F30" s="73">
+      <c r="F30" s="72">
         <f>F27-F28-F29</f>
         <v/>
       </c>
-      <c r="G30" s="73">
+      <c r="G30" s="72">
         <f>G27-G28-G29</f>
         <v/>
       </c>
-      <c r="H30" s="73">
+      <c r="H30" s="72">
         <f>H27-H28-H29</f>
         <v/>
       </c>
-      <c r="I30" s="73">
+      <c r="I30" s="72">
         <f>I27-I28-I29</f>
         <v/>
       </c>
-      <c r="J30" s="73">
+      <c r="J30" s="72">
         <f>J27-J28-J29</f>
         <v/>
       </c>
-      <c r="K30" s="73">
+      <c r="K30" s="72">
         <f>K27-K28-K29</f>
         <v/>
       </c>
-      <c r="L30" s="73">
+      <c r="L30" s="72">
         <f>L27-L28-L29</f>
         <v/>
       </c>
-      <c r="M30" s="73">
+      <c r="M30" s="72">
         <f>M27-M28-M29</f>
         <v/>
       </c>
-      <c r="N30" s="73">
+      <c r="N30" s="72">
         <f>N27-N28-N29</f>
         <v/>
       </c>
-      <c r="O30" s="73">
+      <c r="O30" s="72">
         <f>O27-O28-O29</f>
         <v/>
       </c>
-      <c r="P30" s="73">
+      <c r="P30" s="72">
         <f>P27-P28-P29</f>
         <v/>
       </c>
-      <c r="Q30" s="73">
+      <c r="Q30" s="72">
         <f>Q27-Q28-Q29</f>
         <v/>
       </c>
-      <c r="R30" s="73">
+      <c r="R30" s="72">
         <f>R27-R28-R29</f>
         <v/>
       </c>
-      <c r="S30" s="73">
+      <c r="S30" s="72">
         <f>S27-S28-S29</f>
         <v/>
       </c>
-      <c r="T30" s="73">
+      <c r="T30" s="72">
         <f>T27-T28-T29</f>
         <v/>
       </c>
-      <c r="U30" s="73">
+      <c r="U30" s="72">
         <f>U27-U28-U29</f>
         <v/>
       </c>
-      <c r="V30" s="73">
+      <c r="V30" s="72">
         <f>V27-V28-V29</f>
         <v/>
       </c>
-      <c r="W30" s="73">
+      <c r="W30" s="72">
         <f>W27-W28-W29</f>
         <v/>
       </c>
-      <c r="X30" s="73">
+      <c r="X30" s="72">
         <f>X27-X28-X29</f>
         <v/>
       </c>
-      <c r="Y30" s="73">
+      <c r="Y30" s="72">
         <f>Y27-Y28-Y29</f>
         <v/>
       </c>
-      <c r="Z30" s="73">
+      <c r="Z30" s="72">
         <f>Z27-Z28-Z29</f>
         <v/>
       </c>
-      <c r="AA30" s="74">
+      <c r="AA30" s="73">
         <f>SUM(C30:Z30)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="13" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>Cash Flow (after investment)</t>
         </is>
       </c>
-      <c r="C32" s="68">
+      <c r="C32" s="67">
         <f>C30-$C$15</f>
         <v/>
       </c>
-      <c r="D32" s="68">
+      <c r="D32" s="67">
         <f>D30</f>
         <v/>
       </c>
-      <c r="E32" s="68">
+      <c r="E32" s="67">
         <f>E30</f>
         <v/>
       </c>
-      <c r="F32" s="68">
+      <c r="F32" s="67">
         <f>F30</f>
         <v/>
       </c>
-      <c r="G32" s="68">
+      <c r="G32" s="67">
         <f>G30</f>
         <v/>
       </c>
-      <c r="H32" s="68">
+      <c r="H32" s="67">
         <f>H30</f>
         <v/>
       </c>
-      <c r="I32" s="68">
+      <c r="I32" s="67">
         <f>I30</f>
         <v/>
       </c>
-      <c r="J32" s="68">
+      <c r="J32" s="67">
         <f>J30</f>
         <v/>
       </c>
-      <c r="K32" s="68">
+      <c r="K32" s="67">
         <f>K30</f>
         <v/>
       </c>
-      <c r="L32" s="68">
+      <c r="L32" s="67">
         <f>L30</f>
         <v/>
       </c>
-      <c r="M32" s="68">
+      <c r="M32" s="67">
         <f>M30</f>
         <v/>
       </c>
-      <c r="N32" s="68">
+      <c r="N32" s="67">
         <f>N30</f>
         <v/>
       </c>
-      <c r="O32" s="68">
+      <c r="O32" s="67">
         <f>O30</f>
         <v/>
       </c>
-      <c r="P32" s="68">
+      <c r="P32" s="67">
         <f>P30</f>
         <v/>
       </c>
-      <c r="Q32" s="68">
+      <c r="Q32" s="67">
         <f>Q30</f>
         <v/>
       </c>
-      <c r="R32" s="68">
+      <c r="R32" s="67">
         <f>R30</f>
         <v/>
       </c>
-      <c r="S32" s="68">
+      <c r="S32" s="67">
         <f>S30</f>
         <v/>
       </c>
-      <c r="T32" s="68">
+      <c r="T32" s="67">
         <f>T30</f>
         <v/>
       </c>
-      <c r="U32" s="68">
+      <c r="U32" s="67">
         <f>U30</f>
         <v/>
       </c>
-      <c r="V32" s="68">
+      <c r="V32" s="67">
         <f>V30</f>
         <v/>
       </c>
-      <c r="W32" s="68">
+      <c r="W32" s="67">
         <f>W30</f>
         <v/>
       </c>
-      <c r="X32" s="68">
+      <c r="X32" s="67">
         <f>X30</f>
         <v/>
       </c>
-      <c r="Y32" s="68">
+      <c r="Y32" s="67">
         <f>Y30</f>
         <v/>
       </c>
-      <c r="Z32" s="68">
+      <c r="Z32" s="67">
         <f>Z30</f>
         <v/>
       </c>
-      <c r="AA32" s="69">
+      <c r="AA32" s="68">
         <f>SUM(C32:Z32)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="21" t="inlineStr">
+      <c r="B33" s="25" t="inlineStr">
         <is>
           <t>Cash Position (cumulative)</t>
         </is>
       </c>
-      <c r="C33" s="75">
+      <c r="C33" s="74">
         <f>$C$16+C32</f>
         <v/>
       </c>
-      <c r="D33" s="75">
+      <c r="D33" s="74">
         <f>C33+D32</f>
         <v/>
       </c>
-      <c r="E33" s="75">
+      <c r="E33" s="74">
         <f>D33+E32</f>
         <v/>
       </c>
-      <c r="F33" s="75">
+      <c r="F33" s="74">
         <f>E33+F32</f>
         <v/>
       </c>
-      <c r="G33" s="75">
+      <c r="G33" s="74">
         <f>F33+G32</f>
         <v/>
       </c>
-      <c r="H33" s="75">
+      <c r="H33" s="74">
         <f>G33+H32</f>
         <v/>
       </c>
-      <c r="I33" s="75">
+      <c r="I33" s="74">
         <f>H33+I32</f>
         <v/>
       </c>
-      <c r="J33" s="75">
+      <c r="J33" s="74">
         <f>I33+J32</f>
         <v/>
       </c>
-      <c r="K33" s="75">
+      <c r="K33" s="74">
         <f>J33+K32</f>
         <v/>
       </c>
-      <c r="L33" s="75">
+      <c r="L33" s="74">
         <f>K33+L32</f>
         <v/>
       </c>
-      <c r="M33" s="75">
+      <c r="M33" s="74">
         <f>L33+M32</f>
         <v/>
       </c>
-      <c r="N33" s="75">
+      <c r="N33" s="74">
         <f>M33+N32</f>
         <v/>
       </c>
-      <c r="O33" s="75">
+      <c r="O33" s="74">
         <f>N33+O32</f>
         <v/>
       </c>
-      <c r="P33" s="75">
+      <c r="P33" s="74">
         <f>O33+P32</f>
         <v/>
       </c>
-      <c r="Q33" s="75">
+      <c r="Q33" s="74">
         <f>P33+Q32</f>
         <v/>
       </c>
-      <c r="R33" s="75">
+      <c r="R33" s="74">
         <f>Q33+R32</f>
         <v/>
       </c>
-      <c r="S33" s="75">
+      <c r="S33" s="74">
         <f>R33+S32</f>
         <v/>
       </c>
-      <c r="T33" s="75">
+      <c r="T33" s="74">
         <f>S33+T32</f>
         <v/>
       </c>
-      <c r="U33" s="75">
+      <c r="U33" s="74">
         <f>T33+U32</f>
         <v/>
       </c>
-      <c r="V33" s="75">
+      <c r="V33" s="74">
         <f>U33+V32</f>
         <v/>
       </c>
-      <c r="W33" s="75">
+      <c r="W33" s="74">
         <f>V33+W32</f>
         <v/>
       </c>
-      <c r="X33" s="75">
+      <c r="X33" s="74">
         <f>W33+X32</f>
         <v/>
       </c>
-      <c r="Y33" s="75">
+      <c r="Y33" s="74">
         <f>X33+Y32</f>
         <v/>
       </c>
-      <c r="Z33" s="75">
+      <c r="Z33" s="74">
         <f>Y33+Z32</f>
         <v/>
       </c>
@@ -4050,12 +4131,12 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="17" t="inlineStr">
+      <c r="B37" s="20" t="inlineStr">
         <is>
           <t>NPV (Net Present Value, mil VND)</t>
         </is>
       </c>
-      <c r="C37" s="76">
+      <c r="C37" s="75">
         <f>(NPV($C$17,D32:Z32)+C32)/1000000</f>
         <v/>
       </c>
@@ -4065,12 +4146,12 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="17" t="inlineStr">
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>IRR (Annual)</t>
         </is>
       </c>
-      <c r="C38" s="77">
+      <c r="C38" s="76">
         <f>IFERROR((1+IRR(C32:Z32))^12-1,0)</f>
         <v/>
       </c>
@@ -4080,12 +4161,12 @@
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="17" t="inlineStr">
+      <c r="B39" s="20" t="inlineStr">
         <is>
           <t>Project Payback (months)</t>
         </is>
       </c>
-      <c r="C39" s="25">
+      <c r="C39" s="29">
         <f>IFERROR(MATCH(TRUE(),INDEX(C41:Z41&gt;=0,0),0),"&gt; 24")</f>
         <v/>
       </c>
@@ -4095,12 +4176,12 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="17" t="inlineStr">
+      <c r="B40" s="20" t="inlineStr">
         <is>
           <t>Runway (months until cash = 0)</t>
         </is>
       </c>
-      <c r="C40" s="25">
+      <c r="C40" s="29">
         <f>IFERROR(MATCH(TRUE(),INDEX(C33:Z33&lt;0,0),0)-1,"&gt;= 24")</f>
         <v/>
       </c>
@@ -4110,104 +4191,104 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="26" t="inlineStr">
+      <c r="B41" s="30" t="inlineStr">
         <is>
           <t>(helper: cumulative cash flow)</t>
         </is>
       </c>
-      <c r="C41" s="78">
+      <c r="C41" s="77">
         <f>C32</f>
         <v/>
       </c>
-      <c r="D41" s="78">
+      <c r="D41" s="77">
         <f>C41+D32</f>
         <v/>
       </c>
-      <c r="E41" s="78">
+      <c r="E41" s="77">
         <f>D41+E32</f>
         <v/>
       </c>
-      <c r="F41" s="78">
+      <c r="F41" s="77">
         <f>E41+F32</f>
         <v/>
       </c>
-      <c r="G41" s="78">
+      <c r="G41" s="77">
         <f>F41+G32</f>
         <v/>
       </c>
-      <c r="H41" s="78">
+      <c r="H41" s="77">
         <f>G41+H32</f>
         <v/>
       </c>
-      <c r="I41" s="78">
+      <c r="I41" s="77">
         <f>H41+I32</f>
         <v/>
       </c>
-      <c r="J41" s="78">
+      <c r="J41" s="77">
         <f>I41+J32</f>
         <v/>
       </c>
-      <c r="K41" s="78">
+      <c r="K41" s="77">
         <f>J41+K32</f>
         <v/>
       </c>
-      <c r="L41" s="78">
+      <c r="L41" s="77">
         <f>K41+L32</f>
         <v/>
       </c>
-      <c r="M41" s="78">
+      <c r="M41" s="77">
         <f>L41+M32</f>
         <v/>
       </c>
-      <c r="N41" s="78">
+      <c r="N41" s="77">
         <f>M41+N32</f>
         <v/>
       </c>
-      <c r="O41" s="78">
+      <c r="O41" s="77">
         <f>N41+O32</f>
         <v/>
       </c>
-      <c r="P41" s="78">
+      <c r="P41" s="77">
         <f>O41+P32</f>
         <v/>
       </c>
-      <c r="Q41" s="78">
+      <c r="Q41" s="77">
         <f>P41+Q32</f>
         <v/>
       </c>
-      <c r="R41" s="78">
+      <c r="R41" s="77">
         <f>Q41+R32</f>
         <v/>
       </c>
-      <c r="S41" s="78">
+      <c r="S41" s="77">
         <f>R41+S32</f>
         <v/>
       </c>
-      <c r="T41" s="78">
+      <c r="T41" s="77">
         <f>S41+T32</f>
         <v/>
       </c>
-      <c r="U41" s="78">
+      <c r="U41" s="77">
         <f>T41+U32</f>
         <v/>
       </c>
-      <c r="V41" s="78">
+      <c r="V41" s="77">
         <f>U41+V32</f>
         <v/>
       </c>
-      <c r="W41" s="78">
+      <c r="W41" s="77">
         <f>V41+W32</f>
         <v/>
       </c>
-      <c r="X41" s="78">
+      <c r="X41" s="77">
         <f>W41+X32</f>
         <v/>
       </c>
-      <c r="Y41" s="78">
+      <c r="Y41" s="77">
         <f>X41+Y32</f>
         <v/>
       </c>
-      <c r="Z41" s="78">
+      <c r="Z41" s="77">
         <f>Y41+Z32</f>
         <v/>
       </c>
@@ -4220,12 +4301,12 @@
       </c>
     </row>
     <row r="44" ht="17.6" customHeight="1">
-      <c r="B44" s="17" t="inlineStr">
+      <c r="B44" s="20" t="inlineStr">
         <is>
           <t>Project Decision</t>
         </is>
       </c>
-      <c r="C44" s="28">
+      <c r="C44" s="32">
         <f>IF(AND(C37&gt;0,C38&gt;CHOOSE($C$6,'1. Assumptions'!C35,'1. Assumptions'!D35,'1. Assumptions'!E35)),"✓ GO — NPV+ và IRR &gt; WACC",IF(C37&lt;0,"✗ NO-GO — NPV âm: dự án không tạo giá trị","⚠ HOLD — IRR thấp hơn kỳ vọng, cần điều chỉnh"))</f>
         <v/>
       </c>
@@ -4388,4 +4469,556 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:I30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Tab 4 — SENSITIVITY ANALYSIS  /  Phân tích độ nhạy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Tự động tính từ Tab 1. Câu hỏi: nếu ARPU hoặc Churn xấu đi thì mô hình gãy ở đâu? Giá trị Base hiện tại: ARPU 1.600.000, Churn 3,0%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Bảng 1 — LTV / CAC Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="34" t="inlineStr">
+        <is>
+          <t>ARPU ↓  /  Churn →</t>
+        </is>
+      </c>
+      <c r="C6" s="78" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D6" s="78" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="E6" s="78" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F6" s="78" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="G6" s="78" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H6" s="78" t="n">
+        <v>0.045</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="79" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="C7" s="80">
+        <f>IFERROR((($B7-'1. Assumptions'!$D$15)/C$6)/'1. Assumptions'!$D$22,0)</f>
+        <v/>
+      </c>
+      <c r="D7" s="80">
+        <f>IFERROR((($B7-'1. Assumptions'!$D$15)/D$6)/'1. Assumptions'!$D$22,0)</f>
+        <v/>
+      </c>
+      <c r="E7" s="80">
+        <f>IFERROR((($B7-'1. Assumptions'!$D$15)/E$6)/'1. Assumptions'!$D$22,0)</f>
+        <v/>
+      </c>
+      <c r="F7" s="80">
+        <f>IFERROR((($B7-'1. Assumptions'!$D$15)/F$6)/'1. Assumptions'!$D$22,0)</f>
+        <v/>
+      </c>
+      <c r="G7" s="80">
+        <f>IFERROR((($B7-'1. Assumptions'!$D$15)/G$6)/'1. Assumptions'!$D$22,0)</f>
+        <v/>
+      </c>
+      <c r="H7" s="80">
+        <f>IFERROR((($B7-'1. Assumptions'!$D$15)/H$6)/'1. Assumptions'!$D$22,0)</f>
+        <v/>
+      </c>
+      <c r="I7" s="81" t="inlineStr">
+        <is>
+          <t>Xanh = LTV/CAC ≥ 3,0 (chuẩn vàng VC). Vàng = 1–3, sống ngắc ngoải: đủ trả marketing nhưng không đủ trả lương. Đỏ = &lt; 1, mỗi đồng marketing thu về chưa tới 1 đồng lãi gộp. COGS và CAC lấy từ cột Base của Tab 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="79" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="C8" s="80">
+        <f>IFERROR((($B8-'1. Assumptions'!$D$15)/C$6)/'1. Assumptions'!$D$22,0)</f>
+        <v/>
+      </c>
+      <c r="D8" s="80">
+        <f>IFERROR((($B8-'1. Assumptions'!$D$15)/D$6)/'1. Assumptions'!$D$22,0)</f>
+        <v/>
+      </c>
+      <c r="E8" s="80">
+        <f>IFERROR((($B8-'1. Assumptions'!$D$15)/E$6)/'1. Assumptions'!$D$22,0)</f>
+        <v/>
+      </c>
+      <c r="F8" s="80">
+        <f>IFERROR((($B8-'1. Assumptions'!$D$15)/F$6)/'1. Assumptions'!$D$22,0)</f>
+        <v/>
+      </c>
+      <c r="G8" s="80">
+        <f>IFERROR((($B8-'1. Assumptions'!$D$15)/G$6)/'1. Assumptions'!$D$22,0)</f>
+        <v/>
+      </c>
+      <c r="H8" s="80">
+        <f>IFERROR((($B8-'1. Assumptions'!$D$15)/H$6)/'1. Assumptions'!$D$22,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="79" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="C9" s="80">
+        <f>IFERROR((($B9-'1. Assumptions'!$D$15)/C$6)/'1. Assumptions'!$D$22,0)</f>
+        <v/>
+      </c>
+      <c r="D9" s="80">
+        <f>IFERROR((($B9-'1. Assumptions'!$D$15)/D$6)/'1. Assumptions'!$D$22,0)</f>
+        <v/>
+      </c>
+      <c r="E9" s="80">
+        <f>IFERROR((($B9-'1. Assumptions'!$D$15)/E$6)/'1. Assumptions'!$D$22,0)</f>
+        <v/>
+      </c>
+      <c r="F9" s="80">
+        <f>IFERROR((($B9-'1. Assumptions'!$D$15)/F$6)/'1. Assumptions'!$D$22,0)</f>
+        <v/>
+      </c>
+      <c r="G9" s="80">
+        <f>IFERROR((($B9-'1. Assumptions'!$D$15)/G$6)/'1. Assumptions'!$D$22,0)</f>
+        <v/>
+      </c>
+      <c r="H9" s="80">
+        <f>IFERROR((($B9-'1. Assumptions'!$D$15)/H$6)/'1. Assumptions'!$D$22,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="79" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="C10" s="80">
+        <f>IFERROR((($B10-'1. Assumptions'!$D$15)/C$6)/'1. Assumptions'!$D$22,0)</f>
+        <v/>
+      </c>
+      <c r="D10" s="80">
+        <f>IFERROR((($B10-'1. Assumptions'!$D$15)/D$6)/'1. Assumptions'!$D$22,0)</f>
+        <v/>
+      </c>
+      <c r="E10" s="80">
+        <f>IFERROR((($B10-'1. Assumptions'!$D$15)/E$6)/'1. Assumptions'!$D$22,0)</f>
+        <v/>
+      </c>
+      <c r="F10" s="80">
+        <f>IFERROR((($B10-'1. Assumptions'!$D$15)/F$6)/'1. Assumptions'!$D$22,0)</f>
+        <v/>
+      </c>
+      <c r="G10" s="80">
+        <f>IFERROR((($B10-'1. Assumptions'!$D$15)/G$6)/'1. Assumptions'!$D$22,0)</f>
+        <v/>
+      </c>
+      <c r="H10" s="80">
+        <f>IFERROR((($B10-'1. Assumptions'!$D$15)/H$6)/'1. Assumptions'!$D$22,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="79" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="C11" s="80">
+        <f>IFERROR((($B11-'1. Assumptions'!$D$15)/C$6)/'1. Assumptions'!$D$22,0)</f>
+        <v/>
+      </c>
+      <c r="D11" s="80">
+        <f>IFERROR((($B11-'1. Assumptions'!$D$15)/D$6)/'1. Assumptions'!$D$22,0)</f>
+        <v/>
+      </c>
+      <c r="E11" s="80">
+        <f>IFERROR((($B11-'1. Assumptions'!$D$15)/E$6)/'1. Assumptions'!$D$22,0)</f>
+        <v/>
+      </c>
+      <c r="F11" s="80">
+        <f>IFERROR((($B11-'1. Assumptions'!$D$15)/F$6)/'1. Assumptions'!$D$22,0)</f>
+        <v/>
+      </c>
+      <c r="G11" s="80">
+        <f>IFERROR((($B11-'1. Assumptions'!$D$15)/G$6)/'1. Assumptions'!$D$22,0)</f>
+        <v/>
+      </c>
+      <c r="H11" s="80">
+        <f>IFERROR((($B11-'1. Assumptions'!$D$15)/H$6)/'1. Assumptions'!$D$22,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Bảng 2 — LTV (triệu đồng, tính trên Gross Profit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="34" t="inlineStr">
+        <is>
+          <t>ARPU ↓  /  Churn →</t>
+        </is>
+      </c>
+      <c r="C14" s="78" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D14" s="78" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="E14" s="78" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F14" s="78" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="G14" s="78" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H14" s="78" t="n">
+        <v>0.045</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="79" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="C15" s="82">
+        <f>IFERROR((($B15-'1. Assumptions'!$D$15)/C$14)/1000000,0)</f>
+        <v/>
+      </c>
+      <c r="D15" s="82">
+        <f>IFERROR((($B15-'1. Assumptions'!$D$15)/D$14)/1000000,0)</f>
+        <v/>
+      </c>
+      <c r="E15" s="82">
+        <f>IFERROR((($B15-'1. Assumptions'!$D$15)/E$14)/1000000,0)</f>
+        <v/>
+      </c>
+      <c r="F15" s="82">
+        <f>IFERROR((($B15-'1. Assumptions'!$D$15)/F$14)/1000000,0)</f>
+        <v/>
+      </c>
+      <c r="G15" s="82">
+        <f>IFERROR((($B15-'1. Assumptions'!$D$15)/G$14)/1000000,0)</f>
+        <v/>
+      </c>
+      <c r="H15" s="82">
+        <f>IFERROR((($B15-'1. Assumptions'!$D$15)/H$14)/1000000,0)</f>
+        <v/>
+      </c>
+      <c r="I15" s="81" t="inlineStr">
+        <is>
+          <t>LTV = Gross Profit × số tháng ở lại. Đọc theo hàng ngang thấy rõ: churn xấu đi từ 3,0% lên 4,5% (1,5 lần) làm LTV rơi 33%, trong khi ARPU phải giảm tới 33% mới gây thiệt hại tương đương. Churn là biến nguy hiểm hơn giá.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="79" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="C16" s="82">
+        <f>IFERROR((($B16-'1. Assumptions'!$D$15)/C$14)/1000000,0)</f>
+        <v/>
+      </c>
+      <c r="D16" s="82">
+        <f>IFERROR((($B16-'1. Assumptions'!$D$15)/D$14)/1000000,0)</f>
+        <v/>
+      </c>
+      <c r="E16" s="82">
+        <f>IFERROR((($B16-'1. Assumptions'!$D$15)/E$14)/1000000,0)</f>
+        <v/>
+      </c>
+      <c r="F16" s="82">
+        <f>IFERROR((($B16-'1. Assumptions'!$D$15)/F$14)/1000000,0)</f>
+        <v/>
+      </c>
+      <c r="G16" s="82">
+        <f>IFERROR((($B16-'1. Assumptions'!$D$15)/G$14)/1000000,0)</f>
+        <v/>
+      </c>
+      <c r="H16" s="82">
+        <f>IFERROR((($B16-'1. Assumptions'!$D$15)/H$14)/1000000,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="79" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="C17" s="82">
+        <f>IFERROR((($B17-'1. Assumptions'!$D$15)/C$14)/1000000,0)</f>
+        <v/>
+      </c>
+      <c r="D17" s="82">
+        <f>IFERROR((($B17-'1. Assumptions'!$D$15)/D$14)/1000000,0)</f>
+        <v/>
+      </c>
+      <c r="E17" s="82">
+        <f>IFERROR((($B17-'1. Assumptions'!$D$15)/E$14)/1000000,0)</f>
+        <v/>
+      </c>
+      <c r="F17" s="82">
+        <f>IFERROR((($B17-'1. Assumptions'!$D$15)/F$14)/1000000,0)</f>
+        <v/>
+      </c>
+      <c r="G17" s="82">
+        <f>IFERROR((($B17-'1. Assumptions'!$D$15)/G$14)/1000000,0)</f>
+        <v/>
+      </c>
+      <c r="H17" s="82">
+        <f>IFERROR((($B17-'1. Assumptions'!$D$15)/H$14)/1000000,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="79" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="C18" s="82">
+        <f>IFERROR((($B18-'1. Assumptions'!$D$15)/C$14)/1000000,0)</f>
+        <v/>
+      </c>
+      <c r="D18" s="82">
+        <f>IFERROR((($B18-'1. Assumptions'!$D$15)/D$14)/1000000,0)</f>
+        <v/>
+      </c>
+      <c r="E18" s="82">
+        <f>IFERROR((($B18-'1. Assumptions'!$D$15)/E$14)/1000000,0)</f>
+        <v/>
+      </c>
+      <c r="F18" s="82">
+        <f>IFERROR((($B18-'1. Assumptions'!$D$15)/F$14)/1000000,0)</f>
+        <v/>
+      </c>
+      <c r="G18" s="82">
+        <f>IFERROR((($B18-'1. Assumptions'!$D$15)/G$14)/1000000,0)</f>
+        <v/>
+      </c>
+      <c r="H18" s="82">
+        <f>IFERROR((($B18-'1. Assumptions'!$D$15)/H$14)/1000000,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="79" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="C19" s="82">
+        <f>IFERROR((($B19-'1. Assumptions'!$D$15)/C$14)/1000000,0)</f>
+        <v/>
+      </c>
+      <c r="D19" s="82">
+        <f>IFERROR((($B19-'1. Assumptions'!$D$15)/D$14)/1000000,0)</f>
+        <v/>
+      </c>
+      <c r="E19" s="82">
+        <f>IFERROR((($B19-'1. Assumptions'!$D$15)/E$14)/1000000,0)</f>
+        <v/>
+      </c>
+      <c r="F19" s="82">
+        <f>IFERROR((($B19-'1. Assumptions'!$D$15)/F$14)/1000000,0)</f>
+        <v/>
+      </c>
+      <c r="G19" s="82">
+        <f>IFERROR((($B19-'1. Assumptions'!$D$15)/G$14)/1000000,0)</f>
+        <v/>
+      </c>
+      <c r="H19" s="82">
+        <f>IFERROR((($B19-'1. Assumptions'!$D$15)/H$14)/1000000,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Bảng 3 — Điểm gãy: ARPU tối thiểu để giữ LTV/CAC ≥ 3,0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="34" t="inlineStr">
+        <is>
+          <t>Monthly Churn →</t>
+        </is>
+      </c>
+      <c r="C22" s="78" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D22" s="78" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="E22" s="78" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F22" s="78" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="G22" s="78" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H22" s="78" t="n">
+        <v>0.045</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="83" t="inlineStr">
+        <is>
+          <t>ARPU tối thiểu (VND)</t>
+        </is>
+      </c>
+      <c r="C23" s="84">
+        <f>'1. Assumptions'!$D$15+3*'1. Assumptions'!$D$22*C$22</f>
+        <v/>
+      </c>
+      <c r="D23" s="84">
+        <f>'1. Assumptions'!$D$15+3*'1. Assumptions'!$D$22*D$22</f>
+        <v/>
+      </c>
+      <c r="E23" s="84">
+        <f>'1. Assumptions'!$D$15+3*'1. Assumptions'!$D$22*E$22</f>
+        <v/>
+      </c>
+      <c r="F23" s="84">
+        <f>'1. Assumptions'!$D$15+3*'1. Assumptions'!$D$22*F$22</f>
+        <v/>
+      </c>
+      <c r="G23" s="84">
+        <f>'1. Assumptions'!$D$15+3*'1. Assumptions'!$D$22*G$22</f>
+        <v/>
+      </c>
+      <c r="H23" s="84">
+        <f>'1. Assumptions'!$D$15+3*'1. Assumptions'!$D$22*H$22</f>
+        <v/>
+      </c>
+      <c r="I23" s="81" t="inlineStr">
+        <is>
+          <t>Công thức: ARPU_min = COGS + 3 × CAC × Churn. Nếu churn trượt lên 4,5% mà vẫn muốn giữ chuẩn VC thì phải bán được giá này — nếu không bán nổi thì phải hạ CAC hoặc sửa sản phẩm để giữ chân khách.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26">
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Bảng 4 — Kiểm chứng ROI (không dùng công thức mảng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="85" t="inlineStr">
+        <is>
+          <t>Scenario đang chọn ở Tab 3</t>
+        </is>
+      </c>
+      <c r="C27" s="86">
+        <f>'3. P&amp;L &amp; ROI'!C4</f>
+        <v/>
+      </c>
+      <c r="I27" s="81" t="inlineStr">
+        <is>
+          <t>Đối chiếu chéo với ô C39/C40 của Tab 3. Hai ô đó dùng MATCH(TRUE(),INDEX(...)) — công thức mảng, có bản Excel/WPS không nhận. Bảng này tính cùng kết quả bằng COUNTIF nên chạy được ở mọi phiên bản. Kỳ vọng: Base → Runway 24, Payback 21; Pessimistic → Runway 14, Payback &gt; 24.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="85" t="inlineStr">
+        <is>
+          <t>Số tháng tiền mặt KHÔNG âm (= Runway)</t>
+        </is>
+      </c>
+      <c r="C28" s="87">
+        <f>COUNTIF('3. P&amp;L &amp; ROI'!C33:Z33,"&gt;=0")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="85" t="inlineStr">
+        <is>
+          <t>Project Payback (tháng)</t>
+        </is>
+      </c>
+      <c r="C29" s="86">
+        <f>IF(COUNTIF('3. P&amp;L &amp; ROI'!C41:Z41,"&gt;=0")=0,"&gt; 24",25-COUNTIF('3. P&amp;L &amp; ROI'!C41:Z41,"&gt;=0"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="85" t="inlineStr">
+        <is>
+          <t>Tiền mặt thấp nhất trong 24 tháng (triệu)</t>
+        </is>
+      </c>
+      <c r="C30" s="84">
+        <f>MIN('3. P&amp;L &amp; ROI'!C33:Z33)/1000000</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="I27:I30"/>
+    <mergeCell ref="I23:I25"/>
+    <mergeCell ref="B26:H26"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="I15:I19"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="I7:I11"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C7:H11">
+    <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="25">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="between" dxfId="26">
+      <formula>1</formula>
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="27">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>